--- a/public/qaoa-rqp/QuantumPortfolioOptimizer_demo_0.xlsx
+++ b/public/qaoa-rqp/QuantumPortfolioOptimizer_demo_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhug/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhug/qubit-lab/qubit-lab-new/public/qaoa-rqp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FB9A10-781C-9448-813C-3BBB87C0A38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E81F4A-9DEE-CE46-B696-CFFEB786C37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="660" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53740" yWindow="6020" windowWidth="29400" windowHeight="17500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -83,20 +83,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Search uses Approx Cost USD directly. If Shares is filled and market refresh is enabled, the processor can recompute this value from Shares × Current Price.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -336,9 +322,6 @@
   </si>
   <si>
     <t>Shares</t>
-  </si>
-  <si>
-    <t>Approx Cost USD</t>
   </si>
   <si>
     <t>Expected Return Proxy</t>
@@ -591,6 +574,9 @@
   </si>
   <si>
     <t>Demo Workbook</t>
+  </si>
+  <si>
+    <t>Indicative Market Cost USD</t>
   </si>
 </sst>
 </file>
@@ -697,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -705,36 +691,37 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1046,88 +1033,88 @@
       </c>
     </row>
     <row r="3" spans="1:1" s="5" customFormat="1" ht="35" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="35" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="35" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="64" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1144,12 +1131,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
@@ -1167,7 +1155,7 @@
       <c r="B2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1183,51 +1171,52 @@
         <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
         <v>85</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>87</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
         <v>88</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
       </c>
       <c r="G3">
         <v>498</v>
       </c>
-      <c r="H3" s="3">
-        <v>100040.7272644043</v>
+      <c r="H3" s="15">
+        <f>G3*K3</f>
+        <v>100040.72726440428</v>
       </c>
       <c r="I3" s="4">
         <v>0.97982399608161685</v>
@@ -1250,28 +1239,29 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
         <v>91</v>
       </c>
-      <c r="C4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>372</v>
       </c>
-      <c r="H4" s="3">
-        <v>100033.8175048828</v>
+      <c r="H4" s="15">
+        <f t="shared" ref="H4:H16" si="0">G4*K4</f>
+        <v>100033.81750488281</v>
       </c>
       <c r="I4" s="4">
         <v>0.37110434464841258</v>
@@ -1294,28 +1284,29 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
         <v>93</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
         <v>94</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>95</v>
-      </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5">
         <v>236</v>
       </c>
-      <c r="H5" s="3">
-        <v>100143.5549316406</v>
+      <c r="H5" s="15">
+        <f t="shared" si="0"/>
+        <v>100143.55493164064</v>
       </c>
       <c r="I5" s="4">
         <v>0.16261249299322669</v>
@@ -1338,28 +1329,29 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
         <v>96</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
         <v>97</v>
       </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>248</v>
       </c>
-      <c r="H6" s="3">
-        <v>99993.60302734375</v>
+      <c r="H6" s="15">
+        <f t="shared" si="0"/>
+        <v>99993.603027343735</v>
       </c>
       <c r="I6" s="4">
         <v>1.377138833060616</v>
@@ -1382,28 +1374,29 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
         <v>100</v>
       </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7">
         <v>218</v>
       </c>
-      <c r="H7" s="3">
-        <v>99996.602661132812</v>
+      <c r="H7" s="15">
+        <f t="shared" si="0"/>
+        <v>99996.602661132798</v>
       </c>
       <c r="I7" s="4">
         <v>5.6831100173183851</v>
@@ -1426,28 +1419,29 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
         <v>103</v>
       </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>104</v>
-      </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8">
         <v>550</v>
       </c>
-      <c r="H8" s="3">
-        <v>99910.249328613281</v>
+      <c r="H8" s="15">
+        <f t="shared" si="0"/>
+        <v>99910.249328613296</v>
       </c>
       <c r="I8" s="4">
         <v>0.42650854013064882</v>
@@ -1470,27 +1464,28 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
         <v>105</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
         <v>106</v>
       </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9">
         <v>361</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="15">
+        <f t="shared" si="0"/>
         <v>99903.136474609375</v>
       </c>
       <c r="I9" s="4">
@@ -1514,27 +1509,28 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" t="s">
         <v>108</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>109</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>110</v>
       </c>
-      <c r="D10" t="s">
-        <v>111</v>
-      </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10">
         <v>378</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="15">
+        <f t="shared" si="0"/>
         <v>99895.947692871094</v>
       </c>
       <c r="I10" s="4">
@@ -1558,28 +1554,29 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
         <v>112</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
         <v>113</v>
       </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11">
         <v>1440</v>
       </c>
-      <c r="H11" s="3">
-        <v>100022.1130371094</v>
+      <c r="H11" s="15">
+        <f t="shared" si="0"/>
+        <v>100022.11303710938</v>
       </c>
       <c r="I11" s="4">
         <v>2.6692973904085662</v>
@@ -1602,28 +1599,29 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
         <v>115</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
         <v>116</v>
       </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>117</v>
-      </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12">
         <v>1174</v>
       </c>
-      <c r="H12" s="3">
-        <v>100007.18713378911</v>
+      <c r="H12" s="15">
+        <f t="shared" si="0"/>
+        <v>100007.18713378906</v>
       </c>
       <c r="I12" s="4">
         <v>0.56287192221311599</v>
@@ -1646,28 +1644,29 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" t="s">
         <v>118</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
         <v>119</v>
       </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13">
         <v>254</v>
       </c>
-      <c r="H13" s="3">
-        <v>100082.348449707</v>
+      <c r="H13" s="15">
+        <f t="shared" si="0"/>
+        <v>100082.34844970703</v>
       </c>
       <c r="I13" s="4">
         <v>1.8921131219043661</v>
@@ -1690,28 +1689,29 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" t="s">
         <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" t="s">
-        <v>122</v>
       </c>
       <c r="G14">
         <v>381</v>
       </c>
-      <c r="H14" s="3">
-        <v>150123.52267456049</v>
+      <c r="H14" s="15">
+        <f t="shared" si="0"/>
+        <v>150123.52267456055</v>
       </c>
       <c r="I14" s="4">
         <v>1.8921131219043661</v>
@@ -1734,27 +1734,28 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" t="s">
         <v>123</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
         <v>124</v>
       </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>125</v>
-      </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15">
         <v>57</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="15">
+        <f t="shared" si="0"/>
         <v>99818.9677734375</v>
       </c>
       <c r="I15" s="4">
@@ -1778,27 +1779,28 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
         <v>124</v>
       </c>
-      <c r="C16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G16">
         <v>86</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="15">
+        <f t="shared" si="0"/>
         <v>150604.056640625</v>
       </c>
       <c r="I16" s="4">
@@ -1839,50 +1841,50 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>5.5521447835563578E-2</v>
@@ -1923,7 +1925,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B4">
         <v>2.6831122177774652E-2</v>
@@ -1964,7 +1966,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5">
         <v>2.0462731781641309E-2</v>
@@ -2005,7 +2007,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>2.433165746183906E-2</v>
@@ -2046,7 +2048,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7">
         <v>1.984649410323382E-2</v>
@@ -2087,7 +2089,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8">
         <v>2.5748213732457489E-2</v>
@@ -2128,7 +2130,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9">
         <v>2.787677963322201E-2</v>
@@ -2169,7 +2171,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10">
         <v>3.3058362423824018E-2</v>
@@ -2210,7 +2212,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11">
         <v>1.001561309981959E-2</v>
@@ -2251,7 +2253,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>2.494498662802834E-2</v>
@@ -2292,7 +2294,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13">
         <v>2.3607124548272979E-2</v>
@@ -2333,7 +2335,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14">
         <v>-1.878408050347844E-3</v>
@@ -2631,7 +2633,7 @@
         <v>46</v>
       </c>
       <c r="B23">
-        <v>8000</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
@@ -2664,7 +2666,7 @@
         <v>52</v>
       </c>
       <c r="B26">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
         <v>53</v>
@@ -2675,7 +2677,7 @@
         <v>54</v>
       </c>
       <c r="B27">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
         <v>55</v>
@@ -2686,7 +2688,7 @@
         <v>56</v>
       </c>
       <c r="B28">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
         <v>57</v>
@@ -2734,8 +2736,8 @@
       <c r="B33">
         <v>0</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>143</v>
+      <c r="C33" s="16" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2745,7 +2747,7 @@
       <c r="B34">
         <v>0</v>
       </c>
-      <c r="C34" s="13"/>
+      <c r="C34" s="16"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -2754,7 +2756,7 @@
       <c r="B35">
         <v>16</v>
       </c>
-      <c r="C35" s="13"/>
+      <c r="C35" s="16"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -2763,7 +2765,7 @@
       <c r="B36">
         <v>0</v>
       </c>
-      <c r="C36" s="13"/>
+      <c r="C36" s="16"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -2772,7 +2774,7 @@
       <c r="B37">
         <v>0</v>
       </c>
-      <c r="C37" s="13"/>
+      <c r="C37" s="16"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -2781,7 +2783,7 @@
       <c r="B38">
         <v>16</v>
       </c>
-      <c r="C38" s="13"/>
+      <c r="C38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
